--- a/files/港岛-赤柱-Solace.xlsx
+++ b/files/港岛-赤柱-Solace.xlsx
@@ -8,12 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="52A号屋 销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="52B号屋 销控表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="52C号屋 销控表" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="52D号屋 销控表" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="52E号屋 销控表" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="54号屋 销控表" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="独立屋销控表" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -984,17 +979,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Solace - 52A号屋 销控网格图</t>
+          <t>Solace - 独立屋销控网格图</t>
         </is>
       </c>
     </row>
@@ -1033,665 +1033,136 @@
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
         <is>
+          <t>6 套</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
           <t>1 套</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>0 套</t>
         </is>
       </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
       <c r="D3" s="14" t="inlineStr">
         <is>
-          <t>0 套</t>
+          <t>1 套</t>
         </is>
       </c>
       <c r="E3" s="15" t="inlineStr">
         <is>
-          <t>0 套</t>
+          <t>2 套</t>
         </is>
       </c>
       <c r="F3" s="11" t="inlineStr">
         <is>
-          <t>1 套</t>
+          <t>2 套</t>
         </is>
       </c>
     </row>
     <row r="5" ht="25" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>楼层\房号</t>
+          <t>类型/位置</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
+          <t>52A号屋</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>52B号屋</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>52C号屋</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>52D号屋</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>52E号屋</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>54号屋</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="80" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>-/F</t>
+          <t>独立屋</t>
         </is>
       </c>
       <c r="B6" s="16" t="inlineStr">
         <is>
-          <t>- | 2787呎 (4+房)
+          <t>52A号屋
+2787呎 (4+房)
+(待售)
 暂无价格
-暂无呎价
-(待售)</t>
+暂无呎价</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>52B号屋
+2464呎 (4+房)
+(在售)
+招标项目
+-</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>52C号屋
+2362呎 (4+房)
+(待售)
+暂无价格
+暂无呎价</t>
+        </is>
+      </c>
+      <c r="E6" s="18" t="inlineStr">
+        <is>
+          <t>52D号屋
+2496呎 (4+房)
+(暂停销售)
+暂无价格
+暂无呎价</t>
+        </is>
+      </c>
+      <c r="F6" s="18" t="inlineStr">
+        <is>
+          <t>52E号屋
+2496呎 (4+房)
+(暂停销售)
+暂无价格
+暂无呎价</t>
+        </is>
+      </c>
+      <c r="G6" s="19" t="inlineStr">
+        <is>
+          <t>54号屋
+2784呎 (4+房)
+(25年-07月)
+$1.20亿
+$43,103/呎</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Solace - 52B号屋 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>-/F</t>
-        </is>
-      </c>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>- | 2464呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Solace - 52C号屋 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>-/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>- | 2362呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Solace - 52D号屋 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>-/F</t>
-        </is>
-      </c>
-      <c r="B6" s="18" t="inlineStr">
-        <is>
-          <t>- | 2496呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Solace - 52E号屋 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>-/F</t>
-        </is>
-      </c>
-      <c r="B6" s="18" t="inlineStr">
-        <is>
-          <t>- | 2496呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Solace - 54号屋 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>-/F</t>
-        </is>
-      </c>
-      <c r="B6" s="19" t="inlineStr">
-        <is>
-          <t>- | 2784呎 (4+房)
-$12,000万
-$43,103/呎
-(25年-07月)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>

--- a/files/港岛-赤柱-Solace.xlsx
+++ b/files/港岛-赤柱-Solace.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -98,6 +98,28 @@
       <b val="1"/>
       <color rgb="00000000"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
     </font>
   </fonts>
   <fills count="8">
@@ -217,16 +239,16 @@
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -604,7 +626,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/港岛-赤柱-Solace.xlsx
+++ b/files/港岛-赤柱-Solace.xlsx
@@ -626,7 +626,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/港岛-赤柱-Solace.xlsx
+++ b/files/港岛-赤柱-Solace.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -629,6 +629,10 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -686,6 +690,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -736,6 +760,26 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -786,6 +830,26 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -836,6 +900,26 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -843,7 +927,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>52D号屋</t>
+          <t>52E号屋</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -885,6 +969,26 @@
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -893,7 +997,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>52E号屋</t>
+          <t>54号屋</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -912,75 +1016,45 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>2496</v>
+        <v>2784</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>120000000</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>43103</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>54号屋</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>2784</v>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="n">
-        <v>120000000</v>
-      </c>
-      <c r="I8" s="5" t="n">
-        <v>43103</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -988,7 +1062,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -1001,7 +1075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1010,7 +1084,6 @@
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -1055,7 +1128,7 @@
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>6 套</t>
+          <t>5 套</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
@@ -1075,7 +1148,7 @@
       </c>
       <c r="E3" s="15" t="inlineStr">
         <is>
-          <t>2 套</t>
+          <t>1 套</t>
         </is>
       </c>
       <c r="F3" s="11" t="inlineStr">
@@ -1107,15 +1180,10 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>52D号屋</t>
+          <t>52E号屋</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>52E号屋</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>54号屋</t>
         </is>
@@ -1156,15 +1224,6 @@
       </c>
       <c r="E6" s="18" t="inlineStr">
         <is>
-          <t>52D号屋
-2496呎 (4+房)
-(暂停销售)
-暂无价格
-暂无呎价</t>
-        </is>
-      </c>
-      <c r="F6" s="18" t="inlineStr">
-        <is>
           <t>52E号屋
 2496呎 (4+房)
 (暂停销售)
@@ -1172,11 +1231,11 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="G6" s="19" t="inlineStr">
+      <c r="F6" s="19" t="inlineStr">
         <is>
           <t>54号屋
 2784呎 (4+房)
-(25年-07月)
+(25年-07月-31日)
 $1.20亿
 $43,103/呎</t>
         </is>
@@ -1184,7 +1243,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>

--- a/files/港岛-赤柱-Solace.xlsx
+++ b/files/港岛-赤柱-Solace.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -927,7 +927,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>52E号屋</t>
+          <t>52D号屋</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -997,64 +997,134 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
+          <t>52E号屋</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>2496</v>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
           <t>54号屋</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>4+房</t>
         </is>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="E8" s="4" t="n">
         <v>2784</v>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>已售</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>2025-07-31</t>
         </is>
       </c>
-      <c r="H7" s="5" t="n">
+      <c r="H8" s="5" t="n">
         <v>120000000</v>
       </c>
-      <c r="I7" s="5" t="n">
+      <c r="I8" s="5" t="n">
         <v>43103</v>
       </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N7" s="3" t="inlineStr">
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -1075,7 +1145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1084,6 +1154,7 @@
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -1128,7 +1199,7 @@
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>5 套</t>
+          <t>6 套</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
@@ -1148,7 +1219,7 @@
       </c>
       <c r="E3" s="15" t="inlineStr">
         <is>
-          <t>1 套</t>
+          <t>2 套</t>
         </is>
       </c>
       <c r="F3" s="11" t="inlineStr">
@@ -1180,10 +1251,15 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>52D号屋</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>52E号屋</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>54号屋</t>
         </is>
@@ -1224,6 +1300,15 @@
       </c>
       <c r="E6" s="18" t="inlineStr">
         <is>
+          <t>52D号屋
+2496呎 (4+房)
+(暂停销售)
+暂无价格
+暂无呎价</t>
+        </is>
+      </c>
+      <c r="F6" s="18" t="inlineStr">
+        <is>
           <t>52E号屋
 2496呎 (4+房)
 (暂停销售)
@@ -1231,7 +1316,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="F6" s="19" t="inlineStr">
+      <c r="G6" s="19" t="inlineStr">
         <is>
           <t>54号屋
 2784呎 (4+房)
@@ -1243,7 +1328,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>

--- a/files/港岛-赤柱-Solace.xlsx
+++ b/files/港岛-赤柱-Solace.xlsx
@@ -1320,7 +1320,7 @@
         <is>
           <t>54号屋
 2784呎 (4+房)
-(25年-07月-31日)
+(25年-07月)
 $1.20亿
 $43,103/呎</t>
         </is>

--- a/files/港岛-赤柱-Solace.xlsx
+++ b/files/港岛-赤柱-Solace.xlsx
@@ -1320,7 +1320,7 @@
         <is>
           <t>54号屋
 2784呎 (4+房)
-(25年-07月)
+(25年-07月-31日)
 $1.20亿
 $43,103/呎</t>
         </is>
